--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/6.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/6.xlsx
@@ -426,13 +426,13 @@
         <v>-7.594313250896736</v>
       </c>
       <c r="E2">
-        <v>-15.24300408311629</v>
+        <v>-15.55172827011521</v>
       </c>
       <c r="F2">
-        <v>-4.04303529601093</v>
+        <v>-3.91951577584469</v>
       </c>
       <c r="G2">
-        <v>-9.153474176202966</v>
+        <v>-9.650814122022139</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.288494809785615</v>
       </c>
       <c r="E3">
-        <v>-15.57282190204294</v>
+        <v>-15.45272677135952</v>
       </c>
       <c r="F3">
-        <v>-4.050150143633576</v>
+        <v>-3.556612158515241</v>
       </c>
       <c r="G3">
-        <v>-9.397822231911034</v>
+        <v>-9.00546961677877</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.980226541107653</v>
       </c>
       <c r="E4">
-        <v>-16.43968503896124</v>
+        <v>-15.67740248077608</v>
       </c>
       <c r="F4">
-        <v>-3.388615107390487</v>
+        <v>-3.241051394990589</v>
       </c>
       <c r="G4">
-        <v>-9.489805739719683</v>
+        <v>-9.049443593176909</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.579137773574613</v>
       </c>
       <c r="E5">
-        <v>-17.30338730102218</v>
+        <v>-17.46631273887015</v>
       </c>
       <c r="F5">
-        <v>-3.62861550990138</v>
+        <v>-3.662875128946362</v>
       </c>
       <c r="G5">
-        <v>-9.539659244995569</v>
+        <v>-9.252476040554871</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.08744843100824</v>
       </c>
       <c r="E6">
-        <v>-19.10480067585143</v>
+        <v>-16.99498916415182</v>
       </c>
       <c r="F6">
-        <v>-3.19851058701982</v>
+        <v>-3.253770976460575</v>
       </c>
       <c r="G6">
-        <v>-9.460755702612579</v>
+        <v>-9.888739719384018</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.46983978790643</v>
       </c>
       <c r="E7">
-        <v>-17.99372599264748</v>
+        <v>-18.48390613313375</v>
       </c>
       <c r="F7">
-        <v>-3.042763433047666</v>
+        <v>-3.106247854063414</v>
       </c>
       <c r="G7">
-        <v>-9.520838793604812</v>
+        <v>-9.811762914504886</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.72379281818985</v>
       </c>
       <c r="E8">
-        <v>-19.39325088471801</v>
+        <v>-19.90605075287259</v>
       </c>
       <c r="F8">
-        <v>-3.096425073401018</v>
+        <v>-2.884460765637875</v>
       </c>
       <c r="G8">
-        <v>-9.501551555293018</v>
+        <v>-10.10263406667633</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.8327707345327</v>
       </c>
       <c r="E9">
-        <v>-19.72150638011201</v>
+        <v>-19.77527748047909</v>
       </c>
       <c r="F9">
-        <v>-2.941871596856297</v>
+        <v>-2.490555498258654</v>
       </c>
       <c r="G9">
-        <v>-9.081989566373483</v>
+        <v>-9.221287391029398</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.78356102797001</v>
       </c>
       <c r="E10">
-        <v>-20.71244517636647</v>
+        <v>-20.47849062370819</v>
       </c>
       <c r="F10">
-        <v>-2.688806183668451</v>
+        <v>-2.687098918451281</v>
       </c>
       <c r="G10">
-        <v>-9.539023620252028</v>
+        <v>-8.931240564697232</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.57164443899654</v>
       </c>
       <c r="E11">
-        <v>-21.72289263864597</v>
+        <v>-21.6521805170162</v>
       </c>
       <c r="F11">
-        <v>-2.2733211170789</v>
+        <v>-2.586199626953288</v>
       </c>
       <c r="G11">
-        <v>-8.739424245606319</v>
+        <v>-8.725414016884123</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.19221536600773</v>
       </c>
       <c r="E12">
-        <v>-22.39060254565494</v>
+        <v>-21.99794762139786</v>
       </c>
       <c r="F12">
-        <v>-2.337889042657511</v>
+        <v>-2.240154943005614</v>
       </c>
       <c r="G12">
-        <v>-8.621360260039291</v>
+        <v>-7.836277627583287</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.642885506124381</v>
       </c>
       <c r="E13">
-        <v>-23.52191497919916</v>
+        <v>-23.24553315356303</v>
       </c>
       <c r="F13">
-        <v>-2.18866776708461</v>
+        <v>-2.622247691220914</v>
       </c>
       <c r="G13">
-        <v>-7.999093567750182</v>
+        <v>-7.56599144757503</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.942056112042765</v>
       </c>
       <c r="E14">
-        <v>-24.39659879072871</v>
+        <v>-24.17587643912085</v>
       </c>
       <c r="F14">
-        <v>-2.308978191932405</v>
+        <v>-1.707542039129824</v>
       </c>
       <c r="G14">
-        <v>-7.621549022815079</v>
+        <v>-6.681112419837695</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.105332868306867</v>
       </c>
       <c r="E15">
-        <v>-25.14908173116127</v>
+        <v>-25.94219866886466</v>
       </c>
       <c r="F15">
-        <v>-1.850679784496564</v>
+        <v>-1.887636567805062</v>
       </c>
       <c r="G15">
-        <v>-6.97875032709141</v>
+        <v>-6.088922033772865</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.15907535481765</v>
       </c>
       <c r="E16">
-        <v>-25.8147583533408</v>
+        <v>-26.51256449860475</v>
       </c>
       <c r="F16">
-        <v>-1.713208072164973</v>
+        <v>-1.82477259397401</v>
       </c>
       <c r="G16">
-        <v>-5.964177367307587</v>
+        <v>-6.075974490168775</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.1427038131235</v>
       </c>
       <c r="E17">
-        <v>-26.29774274862888</v>
+        <v>-26.96795237329009</v>
       </c>
       <c r="F17">
-        <v>-1.538338056699191</v>
+        <v>-1.465580890976505</v>
       </c>
       <c r="G17">
-        <v>-6.125069880516167</v>
+        <v>-4.921703129718787</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.089629442325385</v>
       </c>
       <c r="E18">
-        <v>-28.46622064109786</v>
+        <v>-27.35404553871005</v>
       </c>
       <c r="F18">
-        <v>-1.308403974867119</v>
+        <v>-1.381580294495621</v>
       </c>
       <c r="G18">
-        <v>-5.747141312298507</v>
+        <v>-5.140374594224267</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.044479951756128</v>
       </c>
       <c r="E19">
-        <v>-28.23266912262627</v>
+        <v>-28.58069593553776</v>
       </c>
       <c r="F19">
-        <v>-1.208461447719358</v>
+        <v>-1.30228813833225</v>
       </c>
       <c r="G19">
-        <v>-5.180544753797783</v>
+        <v>-4.846156480512618</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.05013163912502</v>
       </c>
       <c r="E20">
-        <v>-28.97553358426654</v>
+        <v>-29.36471064048573</v>
       </c>
       <c r="F20">
-        <v>-0.7991675990983308</v>
+        <v>-0.8455851665142011</v>
       </c>
       <c r="G20">
-        <v>-4.377737460524521</v>
+        <v>-4.187364539288731</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.137004886938443</v>
       </c>
       <c r="E21">
-        <v>-30.12811852446179</v>
+        <v>-30.71616804520184</v>
       </c>
       <c r="F21">
-        <v>-0.5881227791522952</v>
+        <v>-0.4922732153417672</v>
       </c>
       <c r="G21">
-        <v>-3.912592570074761</v>
+        <v>-3.516111704655026</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.345232949802957</v>
       </c>
       <c r="E22">
-        <v>-29.27178635384833</v>
+        <v>-30.67269016625419</v>
       </c>
       <c r="F22">
-        <v>-0.5192125516482099</v>
+        <v>-0.734779429246128</v>
       </c>
       <c r="G22">
-        <v>-4.86554634573613</v>
+        <v>-3.650261630997373</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.6975302950970688</v>
       </c>
       <c r="E23">
-        <v>-30.51245690620379</v>
+        <v>-31.39540065432332</v>
       </c>
       <c r="F23">
-        <v>-0.3881606866883141</v>
+        <v>-0.596089188465018</v>
       </c>
       <c r="G23">
-        <v>-3.137766007699418</v>
+        <v>-3.144651942421103</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.2053255289101139</v>
       </c>
       <c r="E24">
-        <v>-30.82237887457774</v>
+        <v>-30.55012475299959</v>
       </c>
       <c r="F24">
-        <v>-0.4192633975612271</v>
+        <v>-0.4127391758967782</v>
       </c>
       <c r="G24">
-        <v>-2.881695310236792</v>
+        <v>-3.320071129456004</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.1186350480630779</v>
       </c>
       <c r="E25">
-        <v>-32.55565456525057</v>
+        <v>-30.67095349647225</v>
       </c>
       <c r="F25">
-        <v>-0.328996201678165</v>
+        <v>-0.2889015626478633</v>
       </c>
       <c r="G25">
-        <v>-2.860948121342179</v>
+        <v>-3.86544709105</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.2845880874694453</v>
       </c>
       <c r="E26">
-        <v>-31.72861709299273</v>
+        <v>-31.6953033739553</v>
       </c>
       <c r="F26">
-        <v>-0.09618188638655835</v>
+        <v>-0.4088508193080373</v>
       </c>
       <c r="G26">
-        <v>-2.817940824241508</v>
+        <v>-3.510457292873951</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.3043391198717879</v>
       </c>
       <c r="E27">
-        <v>-31.23448585893476</v>
+        <v>-31.56480633847626</v>
       </c>
       <c r="F27">
-        <v>-0.1703240824067253</v>
+        <v>-0.1984943726737281</v>
       </c>
       <c r="G27">
-        <v>-3.224949224476125</v>
+        <v>-3.505587480385683</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.196019372508413</v>
       </c>
       <c r="E28">
-        <v>-32.11062783909478</v>
+        <v>-31.55435688470357</v>
       </c>
       <c r="F28">
-        <v>-0.3555072720373604</v>
+        <v>-0.5313572461406534</v>
       </c>
       <c r="G28">
-        <v>-3.407608574605413</v>
+        <v>-3.583120456915414</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.0118883382582429</v>
       </c>
       <c r="E29">
-        <v>-31.11324955280141</v>
+        <v>-31.85710122177536</v>
       </c>
       <c r="F29">
-        <v>-0.2600569813149817</v>
+        <v>-0.6332895117899382</v>
       </c>
       <c r="G29">
-        <v>-3.638045717957462</v>
+        <v>-2.976519266118137</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.2968474374801984</v>
       </c>
       <c r="E30">
-        <v>-30.95678398312539</v>
+        <v>-30.83518539907143</v>
       </c>
       <c r="F30">
-        <v>-0.2346708338887881</v>
+        <v>-0.244876320291278</v>
       </c>
       <c r="G30">
-        <v>-3.156146156533452</v>
+        <v>-3.337468046264874</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.630727653360589</v>
       </c>
       <c r="E31">
-        <v>-31.48050879482348</v>
+        <v>-31.48060389277764</v>
       </c>
       <c r="F31">
-        <v>-0.4200395778176503</v>
+        <v>-0.6337832187620067</v>
       </c>
       <c r="G31">
-        <v>-3.826806403515627</v>
+        <v>-3.594800061577963</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.9870136129796366</v>
       </c>
       <c r="E32">
-        <v>-31.08897240364629</v>
+        <v>-29.77154195262382</v>
       </c>
       <c r="F32">
-        <v>-0.5707925047183267</v>
+        <v>-0.874787602565092</v>
       </c>
       <c r="G32">
-        <v>-4.182908544992872</v>
+        <v>-4.03092802037601</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.344365688387448</v>
       </c>
       <c r="E33">
-        <v>-29.83262427427628</v>
+        <v>-29.99512177133052</v>
       </c>
       <c r="F33">
-        <v>-0.7108661190621119</v>
+        <v>-0.6690335652207369</v>
       </c>
       <c r="G33">
-        <v>-3.907169896481435</v>
+        <v>-3.186742218407396</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.679428826069185</v>
       </c>
       <c r="E34">
-        <v>-30.34771555027875</v>
+        <v>-30.18705887790863</v>
       </c>
       <c r="F34">
-        <v>-0.549806644935804</v>
+        <v>-0.7248357069429228</v>
       </c>
       <c r="G34">
-        <v>-4.05082439906703</v>
+        <v>-3.797703397679894</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.977144679366077</v>
       </c>
       <c r="E35">
-        <v>-29.03161420637753</v>
+        <v>-29.39203998112202</v>
       </c>
       <c r="F35">
-        <v>-0.7677550788167707</v>
+        <v>-0.3060297154355487</v>
       </c>
       <c r="G35">
-        <v>-3.949707096115531</v>
+        <v>-4.664470430771877</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.225327870460077</v>
       </c>
       <c r="E36">
-        <v>-28.8992921958734</v>
+        <v>-28.70106277466164</v>
       </c>
       <c r="F36">
-        <v>-0.4164726277811956</v>
+        <v>-0.254957551583348</v>
       </c>
       <c r="G36">
-        <v>-5.356844545946131</v>
+        <v>-5.036231452649873</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.415968028146862</v>
       </c>
       <c r="E37">
-        <v>-28.46463567519518</v>
+        <v>-28.27598397650964</v>
       </c>
       <c r="F37">
-        <v>-0.8390659150541689</v>
+        <v>-0.487770210140149</v>
       </c>
       <c r="G37">
-        <v>-4.903369328522303</v>
+        <v>-4.722716168989813</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.548348262651302</v>
       </c>
       <c r="E38">
-        <v>-27.53340933720586</v>
+        <v>-27.73535663557792</v>
       </c>
       <c r="F38">
-        <v>-0.6662013770705654</v>
+        <v>-0.7688418968492436</v>
       </c>
       <c r="G38">
-        <v>-5.349061453383304</v>
+        <v>-5.26822786295092</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.623669983303099</v>
       </c>
       <c r="E39">
-        <v>-27.21575499946382</v>
+        <v>-27.57282517496862</v>
       </c>
       <c r="F39">
-        <v>-0.5966905831994505</v>
+        <v>-0.2689834684475492</v>
       </c>
       <c r="G39">
-        <v>-4.691676494013607</v>
+        <v>-5.169027365866659</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.647534229188132</v>
       </c>
       <c r="E40">
-        <v>-26.66229396319436</v>
+        <v>-26.3400885090746</v>
       </c>
       <c r="F40">
-        <v>-0.4903729405197451</v>
+        <v>-0.4688088802900683</v>
       </c>
       <c r="G40">
-        <v>-5.488955176236287</v>
+        <v>-5.266556037453587</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.630771146255572</v>
       </c>
       <c r="E41">
-        <v>-25.92907515119043</v>
+        <v>-26.45387547546534</v>
       </c>
       <c r="F41">
-        <v>-0.2570177013141103</v>
+        <v>-0.4252152173503416</v>
       </c>
       <c r="G41">
-        <v>-6.368828659118243</v>
+        <v>-5.56180042028241</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.583435926102033</v>
       </c>
       <c r="E42">
-        <v>-24.01736173495636</v>
+        <v>-25.58876485798801</v>
       </c>
       <c r="F42">
-        <v>-0.6988481647822967</v>
+        <v>-0.358867958590518</v>
       </c>
       <c r="G42">
-        <v>-6.290229686924867</v>
+        <v>-5.341486925189452</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.520033206790008</v>
       </c>
       <c r="E43">
-        <v>-24.43495496557368</v>
+        <v>-25.06727937668671</v>
       </c>
       <c r="F43">
-        <v>-0.004177604059825659</v>
+        <v>-0.2918091322316896</v>
       </c>
       <c r="G43">
-        <v>-6.043329200606022</v>
+        <v>-5.227941834283529</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.457860101808504</v>
       </c>
       <c r="E44">
-        <v>-23.6413715950475</v>
+        <v>-22.79463299661929</v>
       </c>
       <c r="F44">
-        <v>0.0478331000597469</v>
+        <v>-0.07618592565038108</v>
       </c>
       <c r="G44">
-        <v>-6.093368096432106</v>
+        <v>-5.78278595611984</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.409154167380818</v>
       </c>
       <c r="E45">
-        <v>-23.40086886897414</v>
+        <v>-22.54418121315107</v>
       </c>
       <c r="F45">
-        <v>-0.2692212098921527</v>
+        <v>-0.2664635748082331</v>
       </c>
       <c r="G45">
-        <v>-6.222982575385651</v>
+        <v>-5.66482459746453</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.392213391469911</v>
       </c>
       <c r="E46">
-        <v>-22.18497359791465</v>
+        <v>-22.5848152104219</v>
       </c>
       <c r="F46">
-        <v>-0.4034556624136041</v>
+        <v>-0.4002159175012553</v>
       </c>
       <c r="G46">
-        <v>-6.179217163356486</v>
+        <v>-5.580389133485418</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.421830074501816</v>
       </c>
       <c r="E47">
-        <v>-21.94989145522846</v>
+        <v>-21.5848194661521</v>
       </c>
       <c r="F47">
-        <v>-0.1773395259410343</v>
+        <v>0.01839540766646087</v>
       </c>
       <c r="G47">
-        <v>-6.513396872272677</v>
+        <v>-5.482115589152152</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.505977963297771</v>
       </c>
       <c r="E48">
-        <v>-21.14682093165622</v>
+        <v>-21.12256189639713</v>
       </c>
       <c r="F48">
-        <v>-0.1130275658898891</v>
+        <v>-0.07193474413921402</v>
       </c>
       <c r="G48">
-        <v>-6.177091793120274</v>
+        <v>-5.796961712119</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.657245309377768</v>
       </c>
       <c r="E49">
-        <v>-20.24902831726553</v>
+        <v>-20.40650600088227</v>
       </c>
       <c r="F49">
-        <v>-0.1714514904419354</v>
+        <v>-0.08056798921119047</v>
       </c>
       <c r="G49">
-        <v>-6.607800388870534</v>
+        <v>-5.930926247911147</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.877821962899159</v>
       </c>
       <c r="E50">
-        <v>-20.67059301958758</v>
+        <v>-19.83003578817983</v>
       </c>
       <c r="F50">
-        <v>0.01538015032027067</v>
+        <v>0.05022625348643467</v>
       </c>
       <c r="G50">
-        <v>-6.828001325415157</v>
+        <v>-6.429520890489703</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.167048020289583</v>
       </c>
       <c r="E51">
-        <v>-20.10150421951765</v>
+        <v>-18.31322341931065</v>
       </c>
       <c r="F51">
-        <v>-0.2992926033485803</v>
+        <v>0.2261151608576593</v>
       </c>
       <c r="G51">
-        <v>-7.043514529476172</v>
+        <v>-6.079728648810309</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.526986394664215</v>
       </c>
       <c r="E52">
-        <v>-17.96199950374974</v>
+        <v>-17.83224513800797</v>
       </c>
       <c r="F52">
-        <v>-0.219107467124991</v>
+        <v>-0.1054156978255644</v>
       </c>
       <c r="G52">
-        <v>-6.657279802500481</v>
+        <v>-6.751865399102998</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.94386785509536</v>
       </c>
       <c r="E53">
-        <v>-17.6471754622625</v>
+        <v>-17.18931956924298</v>
       </c>
       <c r="F53">
-        <v>0.1386842949617827</v>
+        <v>-0.1417727431344347</v>
       </c>
       <c r="G53">
-        <v>-6.921448094352165</v>
+        <v>-7.388900435042796</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.408722923462738</v>
       </c>
       <c r="E54">
-        <v>-17.64571729363202</v>
+        <v>-17.32831655043441</v>
       </c>
       <c r="F54">
-        <v>-0.1837336939232437</v>
+        <v>-0.1470361896118228</v>
       </c>
       <c r="G54">
-        <v>-6.439757097297129</v>
+        <v>-6.35253746451949</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.908968536055355</v>
       </c>
       <c r="E55">
-        <v>-16.4500507159648</v>
+        <v>-16.58607248973319</v>
       </c>
       <c r="F55">
-        <v>-0.07907361441654016</v>
+        <v>-0.3813092598997594</v>
       </c>
       <c r="G55">
-        <v>-7.184560322176822</v>
+        <v>-6.656581277391695</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.419693474183026</v>
       </c>
       <c r="E56">
-        <v>-16.95104938085539</v>
+        <v>-16.8381137675781</v>
       </c>
       <c r="F56">
-        <v>-0.5991110727504306</v>
+        <v>0.1432502560860135</v>
       </c>
       <c r="G56">
-        <v>-6.675825478611478</v>
+        <v>-7.285525340033514</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.92558444678276</v>
       </c>
       <c r="E57">
-        <v>-16.03307335781252</v>
+        <v>-15.62127657392501</v>
       </c>
       <c r="F57">
-        <v>-0.2356441655870775</v>
+        <v>0.04386770530254567</v>
       </c>
       <c r="G57">
-        <v>-8.299409706345168</v>
+        <v>-7.257170517489656</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.405539461777475</v>
       </c>
       <c r="E58">
-        <v>-15.62605864247711</v>
+        <v>-15.67174188826649</v>
       </c>
       <c r="F58">
-        <v>-0.4156334916021597</v>
+        <v>-0.5652871749593211</v>
       </c>
       <c r="G58">
-        <v>-7.504888708556702</v>
+        <v>-7.323258938090127</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.837066057944432</v>
       </c>
       <c r="E59">
-        <v>-15.34504418793113</v>
+        <v>-15.01338328008336</v>
       </c>
       <c r="F59">
-        <v>-0.2960843363975378</v>
+        <v>-0.3137517563644457</v>
       </c>
       <c r="G59">
-        <v>-7.650936735567189</v>
+        <v>-8.533220295601735</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.209865140711702</v>
       </c>
       <c r="E60">
-        <v>-14.63055967289693</v>
+        <v>-14.91223528464804</v>
       </c>
       <c r="F60">
-        <v>-0.4440787998468919</v>
+        <v>-0.2245208481022858</v>
       </c>
       <c r="G60">
-        <v>-7.370033636014489</v>
+        <v>-7.547008779452849</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.508626918633134</v>
       </c>
       <c r="E61">
-        <v>-14.26288833974017</v>
+        <v>-14.467656877419</v>
       </c>
       <c r="F61">
-        <v>-0.6021636066297468</v>
+        <v>-0.417115440885768</v>
       </c>
       <c r="G61">
-        <v>-7.731382992171478</v>
+        <v>-8.075855187169264</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.724437116157538</v>
       </c>
       <c r="E62">
-        <v>-14.39062753454853</v>
+        <v>-13.75852954713588</v>
       </c>
       <c r="F62">
-        <v>-0.5870467298960586</v>
+        <v>-0.5445564523368608</v>
       </c>
       <c r="G62">
-        <v>-8.551216421153214</v>
+        <v>-7.804089193304953</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.857120997222807</v>
       </c>
       <c r="E63">
-        <v>-14.26500313710175</v>
+        <v>-13.45046198886807</v>
       </c>
       <c r="F63">
-        <v>-0.6230972792658931</v>
+        <v>-0.3007472165078963</v>
       </c>
       <c r="G63">
-        <v>-8.195862462967844</v>
+        <v>-7.760578693282311</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.900170131470434</v>
       </c>
       <c r="E64">
-        <v>-13.51444932659646</v>
+        <v>-14.12301736306525</v>
       </c>
       <c r="F64">
-        <v>-1.147990627314994</v>
+        <v>-0.5799037177817185</v>
       </c>
       <c r="G64">
-        <v>-8.1066697450488</v>
+        <v>-7.885594824481809</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.857693574968804</v>
       </c>
       <c r="E65">
-        <v>-13.1376893461063</v>
+        <v>-13.00861425146567</v>
       </c>
       <c r="F65">
-        <v>-0.9682713490732247</v>
+        <v>-0.4585304975561321</v>
       </c>
       <c r="G65">
-        <v>-8.723076771733398</v>
+        <v>-8.546608141762547</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.73796852137974</v>
       </c>
       <c r="E66">
-        <v>-12.57353205423072</v>
+        <v>-13.11528698519035</v>
       </c>
       <c r="F66">
-        <v>-0.9108207562194678</v>
+        <v>-0.8337552516348213</v>
       </c>
       <c r="G66">
-        <v>-8.245262423504849</v>
+        <v>-8.850158683349402</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.544088081559185</v>
       </c>
       <c r="E67">
-        <v>-12.04898985297425</v>
+        <v>-12.8839408335605</v>
       </c>
       <c r="F67">
-        <v>-1.132281467888304</v>
+        <v>-0.7780243495092762</v>
       </c>
       <c r="G67">
-        <v>-8.166471439670195</v>
+        <v>-7.955079864805572</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.288984004761445</v>
       </c>
       <c r="E68">
-        <v>-13.08275895639326</v>
+        <v>-11.85311976672049</v>
       </c>
       <c r="F68">
-        <v>-1.057327471813394</v>
+        <v>-0.7981561624995126</v>
       </c>
       <c r="G68">
-        <v>-8.550484790589035</v>
+        <v>-7.732412571834192</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.984258672532731</v>
       </c>
       <c r="E69">
-        <v>-13.27953926592257</v>
+        <v>-12.84719226698825</v>
       </c>
       <c r="F69">
-        <v>-1.066366616912742</v>
+        <v>-0.7621768527263189</v>
       </c>
       <c r="G69">
-        <v>-8.125447159347546</v>
+        <v>-8.244494376939738</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.635650783718109</v>
       </c>
       <c r="E70">
-        <v>-12.85314268183433</v>
+        <v>-12.30554601940481</v>
       </c>
       <c r="F70">
-        <v>-1.014840507723807</v>
+        <v>-1.268396314414111</v>
       </c>
       <c r="G70">
-        <v>-8.015090123795941</v>
+        <v>-7.876768910074112</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.25724379573118</v>
       </c>
       <c r="E71">
-        <v>-12.73519857630456</v>
+        <v>-13.07713459167573</v>
       </c>
       <c r="F71">
-        <v>-1.137570593755179</v>
+        <v>-1.282388268214797</v>
       </c>
       <c r="G71">
-        <v>-8.335090766167433</v>
+        <v>-6.727655379574308</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.855471406224031</v>
       </c>
       <c r="E72">
-        <v>-13.02162908576372</v>
+        <v>-12.7192855186416</v>
       </c>
       <c r="F72">
-        <v>-1.360543075934125</v>
+        <v>-1.067678750878777</v>
       </c>
       <c r="G72">
-        <v>-8.37693937232936</v>
+        <v>-6.426653958052693</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.431271818046273</v>
       </c>
       <c r="E73">
-        <v>-13.26744824032209</v>
+        <v>-12.95273741068503</v>
       </c>
       <c r="F73">
-        <v>-1.799834593312731</v>
+        <v>-1.56901332999226</v>
       </c>
       <c r="G73">
-        <v>-7.182034375930357</v>
+        <v>-7.774535953275879</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.995415656742643</v>
       </c>
       <c r="E74">
-        <v>-13.44233790649831</v>
+        <v>-13.58275230005415</v>
       </c>
       <c r="F74">
-        <v>-1.890466270853025</v>
+        <v>-1.350634145061837</v>
       </c>
       <c r="G74">
-        <v>-7.573969862324673</v>
+        <v>-6.460063983635018</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.548012119386194</v>
       </c>
       <c r="E75">
-        <v>-13.83049152759177</v>
+        <v>-12.37026696992243</v>
       </c>
       <c r="F75">
-        <v>-1.499990444521394</v>
+        <v>-1.59126493516626</v>
       </c>
       <c r="G75">
-        <v>-6.836284310354413</v>
+        <v>-6.54813442661625</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.090627941854341</v>
       </c>
       <c r="E76">
-        <v>-13.30607612360751</v>
+        <v>-12.64064856749841</v>
       </c>
       <c r="F76">
-        <v>-1.226528140774415</v>
+        <v>-1.332819275697231</v>
       </c>
       <c r="G76">
-        <v>-6.605118846983724</v>
+        <v>-6.780693629658972</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.630616894347193</v>
       </c>
       <c r="E77">
-        <v>-13.87796804908819</v>
+        <v>-14.37826480050759</v>
       </c>
       <c r="F77">
-        <v>-1.720866328803854</v>
+        <v>-1.648554824743874</v>
       </c>
       <c r="G77">
-        <v>-6.361015771645564</v>
+        <v>-6.314572128275128</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.166903030478168</v>
       </c>
       <c r="E78">
-        <v>-14.64071704009614</v>
+        <v>-14.20878213229652</v>
       </c>
       <c r="F78">
-        <v>-1.194013891847132</v>
+        <v>-1.445099506942287</v>
       </c>
       <c r="G78">
-        <v>-6.078073376040673</v>
+        <v>-5.235562710114931</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.706324695089803</v>
       </c>
       <c r="E79">
-        <v>-15.20222517467722</v>
+        <v>-15.11419163996811</v>
       </c>
       <c r="F79">
-        <v>-1.501931309346153</v>
+        <v>-1.54464027589969</v>
       </c>
       <c r="G79">
-        <v>-6.287465381399576</v>
+        <v>-5.428375503413164</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.257151976832081</v>
       </c>
       <c r="E80">
-        <v>-16.02218237782407</v>
+        <v>-15.11254327542932</v>
       </c>
       <c r="F80">
-        <v>-1.904261901579248</v>
+        <v>-1.696911600249698</v>
       </c>
       <c r="G80">
-        <v>-5.287690560176295</v>
+        <v>-5.134895641356772</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.823748680033922</v>
       </c>
       <c r="E81">
-        <v>-16.46300215162674</v>
+        <v>-16.1631854730009</v>
       </c>
       <c r="F81">
-        <v>-1.693540144920304</v>
+        <v>-1.574508719342432</v>
       </c>
       <c r="G81">
-        <v>-5.605552590129418</v>
+        <v>-4.997127288740002</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.421265756736923</v>
       </c>
       <c r="E82">
-        <v>-16.89876361996283</v>
+        <v>-17.18477298133928</v>
       </c>
       <c r="F82">
-        <v>-1.843790252807481</v>
+        <v>-2.031121399113575</v>
       </c>
       <c r="G82">
-        <v>-4.666095908631658</v>
+        <v>-4.614762589499719</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.060010931687851</v>
       </c>
       <c r="E83">
-        <v>-17.50617689555967</v>
+        <v>-17.69613732323343</v>
       </c>
       <c r="F83">
-        <v>-1.645029293077559</v>
+        <v>-1.778506617792852</v>
       </c>
       <c r="G83">
-        <v>-4.518783253225169</v>
+        <v>-3.59990161225398</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.7493339568146021</v>
       </c>
       <c r="E84">
-        <v>-18.48226682554298</v>
+        <v>-17.73070316533397</v>
       </c>
       <c r="F84">
-        <v>-1.819306197482936</v>
+        <v>-1.707360626668611</v>
       </c>
       <c r="G84">
-        <v>-4.708696008631</v>
+        <v>-3.787844593063944</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.505607307242111</v>
       </c>
       <c r="E85">
-        <v>-18.98724601908631</v>
+        <v>-18.97192166304436</v>
       </c>
       <c r="F85">
-        <v>-1.989169560366197</v>
+        <v>-1.66475106420341</v>
       </c>
       <c r="G85">
-        <v>-4.431272292440075</v>
+        <v>-3.268949685238578</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.3347129957690748</v>
       </c>
       <c r="E86">
-        <v>-21.31061583651365</v>
+        <v>-19.51033005171232</v>
       </c>
       <c r="F86">
-        <v>-1.76007461471316</v>
+        <v>-2.221185329481505</v>
       </c>
       <c r="G86">
-        <v>-4.146734213885255</v>
+        <v>-2.967656935709508</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.2468203671885719</v>
       </c>
       <c r="E87">
-        <v>-21.37337595778596</v>
+        <v>-20.34567953801124</v>
       </c>
       <c r="F87">
-        <v>-1.97525133126436</v>
+        <v>-1.90047212071144</v>
       </c>
       <c r="G87">
-        <v>-4.009972267112423</v>
+        <v>-3.455237393278908</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.2497550935749764</v>
       </c>
       <c r="E88">
-        <v>-22.48717678234252</v>
+        <v>-22.07047566110471</v>
       </c>
       <c r="F88">
-        <v>-1.798921732434846</v>
+        <v>-1.901495154453897</v>
       </c>
       <c r="G88">
-        <v>-3.729327390111787</v>
+        <v>-3.314615350407285</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.3445603785076087</v>
       </c>
       <c r="E89">
-        <v>-23.66188105382824</v>
+        <v>-24.07465145962739</v>
       </c>
       <c r="F89">
-        <v>-2.005465203914069</v>
+        <v>-1.900006578231067</v>
       </c>
       <c r="G89">
-        <v>-3.35156765971663</v>
+        <v>-2.934084693395759</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.5383738091687614</v>
       </c>
       <c r="E90">
-        <v>-25.71541721903453</v>
+        <v>-25.57754782787101</v>
       </c>
       <c r="F90">
-        <v>-2.323506927810105</v>
+        <v>-1.87733002057943</v>
       </c>
       <c r="G90">
-        <v>-3.637244565936959</v>
+        <v>-3.243388963129866</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.8286885890158798</v>
       </c>
       <c r="E91">
-        <v>-27.53488561973236</v>
+        <v>-26.66819003635235</v>
       </c>
       <c r="F91">
-        <v>-2.031654867720978</v>
+        <v>-1.718121947598379</v>
       </c>
       <c r="G91">
-        <v>-3.509523719031876</v>
+        <v>-2.619794742079509</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.212512289124607</v>
       </c>
       <c r="E92">
-        <v>-29.06478980695772</v>
+        <v>-28.73831853032274</v>
       </c>
       <c r="F92">
-        <v>-2.470091509939895</v>
+        <v>-2.042312642725396</v>
       </c>
       <c r="G92">
-        <v>-3.102002184238672</v>
+        <v>-3.150458639296984</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.68913064877086</v>
       </c>
       <c r="E93">
-        <v>-31.11408505625583</v>
+        <v>-30.50223840460548</v>
       </c>
       <c r="F93">
-        <v>-2.374907125153815</v>
+        <v>-2.687715223798964</v>
       </c>
       <c r="G93">
-        <v>-3.80244409889213</v>
+        <v>-3.136249777842432</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.243507543602886</v>
       </c>
       <c r="E94">
-        <v>-32.81501385709187</v>
+        <v>-31.0009524543592</v>
       </c>
       <c r="F94">
-        <v>-2.092690634694051</v>
+        <v>-2.131695142222269</v>
       </c>
       <c r="G94">
-        <v>-3.329353899148121</v>
+        <v>-3.730390075229893</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.867933658227281</v>
       </c>
       <c r="E95">
-        <v>-34.54311803044795</v>
+        <v>-33.78161889826612</v>
       </c>
       <c r="F95">
-        <v>-2.025019644824554</v>
+        <v>-2.513673575735982</v>
       </c>
       <c r="G95">
-        <v>-4.017828191677114</v>
+        <v>-4.215600182193175</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.554229492279845</v>
       </c>
       <c r="E96">
-        <v>-35.8434127358254</v>
+        <v>-36.43758701766081</v>
       </c>
       <c r="F96">
-        <v>-2.704892250263415</v>
+        <v>-2.68918474757153</v>
       </c>
       <c r="G96">
-        <v>-3.565256753185507</v>
+        <v>-4.370080168692186</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.274000156681026</v>
       </c>
       <c r="E97">
-        <v>-37.35494263976463</v>
+        <v>-38.36978045759457</v>
       </c>
       <c r="F97">
-        <v>-2.499072771894238</v>
+        <v>-2.672988508111994</v>
       </c>
       <c r="G97">
-        <v>-4.509642836991241</v>
+        <v>-4.517065080090287</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.030038415934776</v>
       </c>
       <c r="E98">
-        <v>-39.67300282141797</v>
+        <v>-40.22653631327156</v>
       </c>
       <c r="F98">
-        <v>-2.590990075643677</v>
+        <v>-2.49776560813262</v>
       </c>
       <c r="G98">
-        <v>-4.443584211300624</v>
+        <v>-4.866870563951838</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.781495722866786</v>
       </c>
       <c r="E99">
-        <v>-42.27558702497325</v>
+        <v>-42.00613829304286</v>
       </c>
       <c r="F99">
-        <v>-2.664831574296628</v>
+        <v>-2.985302899785075</v>
       </c>
       <c r="G99">
-        <v>-5.256031813184245</v>
+        <v>-5.327291305917057</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.54617282519073</v>
       </c>
       <c r="E100">
-        <v>-44.7818641718074</v>
+        <v>-44.80869085182884</v>
       </c>
       <c r="F100">
-        <v>-2.674424897188449</v>
+        <v>-2.988516965307937</v>
       </c>
       <c r="G100">
-        <v>-5.587582948942254</v>
+        <v>-6.175320651256764</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.260929333306814</v>
       </c>
       <c r="E101">
-        <v>-46.87878764648118</v>
+        <v>-45.93786131716743</v>
       </c>
       <c r="F101">
-        <v>-2.463376763772802</v>
+        <v>-3.43068954451348</v>
       </c>
       <c r="G101">
-        <v>-6.249460318608742</v>
+        <v>-6.576459454250254</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.004068150939673</v>
       </c>
       <c r="E102">
-        <v>-49.44155863867952</v>
+        <v>-48.58616273006714</v>
       </c>
       <c r="F102">
-        <v>-2.780644792514624</v>
+        <v>-3.648076345295348</v>
       </c>
       <c r="G102">
-        <v>-6.008889595360984</v>
+        <v>-5.906769197111085</v>
       </c>
     </row>
   </sheetData>
